--- a/draft/draft-board/2026_ESPN_FullPPR_Draft_Board.xlsx
+++ b/draft/draft-board/2026_ESPN_FullPPR_Draft_Board.xlsx
@@ -25412,17 +25412,17 @@
   </mergeCells>
   <conditionalFormatting sqref="A3:A180">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="17" text="" percent="0" bottom="0">
-      <formula>$A3="★"</formula>
+      <formula>OR($A3="★",$A3="☑")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:N180">
     <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="18" text="" percent="0" bottom="0">
-      <formula>$A3="★"</formula>
+      <formula>OR($A3="★",$A3="☑")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="A3:A180" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"☐,★"</formula1>
+      <formula1>"☐,☑,★"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
